--- a/output/pdf_financials_xlsx/GGA.xlsx
+++ b/output/pdf_financials_xlsx/GGA.xlsx
@@ -4151,28 +4151,28 @@
         </is>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>7.915</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>8.036</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>8.271000000000001</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>8.444000000000001</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>8.519</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>8.664</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>9.613</v>
       </c>
     </row>
     <row r="93">
@@ -7330,7 +7330,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
           <t>-</t>
@@ -10024,7 +10028,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr"/>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E67" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/GGA.xlsx
+++ b/output/pdf_financials_xlsx/GGA.xlsx
@@ -1768,13 +1768,13 @@
         <v>0.459</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.292</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.366</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>9.611000000000001</v>
       </c>
     </row>
     <row r="35">
@@ -1850,13 +1850,13 @@
         <v>0.459</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.292</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.366</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>9.611000000000001</v>
       </c>
     </row>
     <row r="37">
@@ -2342,13 +2342,13 @@
         <v>0.354</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.44</v>
+        <v>0.148</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.049</v>
+        <v>0</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>16.025</v>
+        <v>6.414</v>
       </c>
     </row>
     <row r="49">
@@ -5331,22 +5331,22 @@
         <v>0</v>
       </c>
       <c r="F124" s="3" t="n">
-        <v>0</v>
+        <v>-0.3</v>
       </c>
       <c r="G124" s="3" t="n">
-        <v>0</v>
+        <v>-0.102</v>
       </c>
       <c r="H124" s="3" t="n">
-        <v>0</v>
+        <v>-0.083</v>
       </c>
       <c r="I124" s="3" t="n">
-        <v>0</v>
+        <v>-0.091</v>
       </c>
       <c r="J124" s="3" t="n">
-        <v>0</v>
+        <v>-0.063</v>
       </c>
       <c r="K124" s="3" t="n">
-        <v>0</v>
+        <v>-0.013</v>
       </c>
     </row>
     <row r="125">
@@ -5368,22 +5368,22 @@
         <v>0</v>
       </c>
       <c r="F125" s="3" t="n">
-        <v>0</v>
+        <v>-0.3</v>
       </c>
       <c r="G125" s="3" t="n">
-        <v>0</v>
+        <v>-0.102</v>
       </c>
       <c r="H125" s="3" t="n">
-        <v>0</v>
+        <v>-0.083</v>
       </c>
       <c r="I125" s="3" t="n">
-        <v>0</v>
+        <v>-0.091</v>
       </c>
       <c r="J125" s="3" t="n">
-        <v>0</v>
+        <v>-0.063</v>
       </c>
       <c r="K125" s="3" t="n">
-        <v>0</v>
+        <v>-0.013</v>
       </c>
     </row>
     <row r="126">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -13352,7 +13352,11 @@
           <t>Lease payments 16</t>
         </is>
       </c>
-      <c r="D119" t="inlineStr"/>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E119" t="inlineStr">
         <is>
           <t>-</t>
@@ -16146,7 +16150,11 @@
           <t>Lease payments 14</t>
         </is>
       </c>
-      <c r="D162" t="inlineStr"/>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E162" t="inlineStr">
         <is>
           <t>-</t>
@@ -18564,7 +18572,11 @@
           <t>Lease payments 15</t>
         </is>
       </c>
-      <c r="D199" t="inlineStr"/>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E199" t="inlineStr">
         <is>
           <t>-</t>
